--- a/pages/WR_progressions/Medals_Women_TS.xlsx
+++ b/pages/WR_progressions/Medals_Women_TS.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SamB\CNZPD\pages\WR_progressions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E44E1B2B-A730-4019-B150-6A40AA05C082}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59D179CE-5655-40B2-AE54-32CC60F0F4A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{60BF7A36-0D27-46A2-BCFD-CC0E6E4E1F78}"/>
+    <workbookView xWindow="3218" yWindow="1440" windowWidth="14400" windowHeight="8190" xr2:uid="{60BF7A36-0D27-46A2-BCFD-CC0E6E4E1F78}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="8">
   <si>
     <t>Year</t>
   </si>
@@ -57,25 +57,22 @@
   </si>
   <si>
     <t>8th</t>
+  </si>
+  <si>
+    <t>OLY</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="6"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -100,7 +97,9 @@
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -435,7 +434,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C1A844C-89A8-4AB0-8288-D746F85E52AB}">
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="4.73046875" bestFit="1" customWidth="1"/>
@@ -444,7 +443,7 @@
     <col min="5" max="5" width="10.73046875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -464,65 +463,92 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A2">
+        <v>2024</v>
+      </c>
+      <c r="B2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="1">
+        <v>45.472000000000001</v>
+      </c>
+      <c r="D2" s="1">
+        <v>45.593000000000004</v>
+      </c>
+      <c r="E2" s="1">
+        <v>45.643999999999998</v>
+      </c>
+      <c r="F2" s="1">
+        <v>47.578000000000003</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A3">
         <v>2023</v>
-      </c>
-      <c r="B2" t="s">
-        <v>2</v>
-      </c>
-      <c r="C2" s="1">
-        <v>46.072000000000003</v>
-      </c>
-      <c r="D2" s="1">
-        <v>46.466999999999999</v>
-      </c>
-      <c r="E2">
-        <v>46.679000000000002</v>
-      </c>
-      <c r="F2" s="1">
-        <v>47.436</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A3">
-        <v>2022</v>
       </c>
       <c r="B3" t="s">
         <v>2</v>
       </c>
       <c r="C3">
-        <v>46.573</v>
+        <v>46.072000000000003</v>
       </c>
       <c r="D3">
-        <v>46.643000000000001</v>
+        <v>46.466999999999999</v>
       </c>
       <c r="E3">
-        <v>46.985999999999997</v>
+        <v>46.679000000000002</v>
       </c>
       <c r="F3">
-        <v>48.73</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.45">
+        <v>47.436</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A4">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="B4" t="s">
         <v>2</v>
       </c>
       <c r="C4">
+        <v>46.573</v>
+      </c>
+      <c r="D4">
+        <v>46.643000000000001</v>
+      </c>
+      <c r="E4">
+        <v>46.985999999999997</v>
+      </c>
+      <c r="F4">
+        <v>48.73</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A5">
+        <v>2021</v>
+      </c>
+      <c r="B5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C5">
         <v>46.511000000000003</v>
       </c>
-      <c r="D4" s="1">
+      <c r="D5">
         <v>47.030999999999999</v>
       </c>
-      <c r="E4" s="1">
+      <c r="E5">
         <v>48.362000000000002</v>
       </c>
-      <c r="F4" s="1">
+      <c r="F5">
         <v>55.652999999999999</v>
       </c>
+      <c r="I5" s="1"/>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="I6" s="1"/>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="I7" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/pages/WR_progressions/Medals_Women_TS.xlsx
+++ b/pages/WR_progressions/Medals_Women_TS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SamB\CNZPD\pages\WR_progressions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59D179CE-5655-40B2-AE54-32CC60F0F4A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFF8707B-A114-4D72-9336-E3BCC544AD0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3218" yWindow="1440" windowWidth="14400" windowHeight="8190" xr2:uid="{60BF7A36-0D27-46A2-BCFD-CC0E6E4E1F78}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{60BF7A36-0D27-46A2-BCFD-CC0E6E4E1F78}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -536,12 +536,6 @@
       <c r="D5">
         <v>47.030999999999999</v>
       </c>
-      <c r="E5">
-        <v>48.362000000000002</v>
-      </c>
-      <c r="F5">
-        <v>55.652999999999999</v>
-      </c>
       <c r="I5" s="1"/>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.45">

--- a/pages/WR_progressions/Medals_Women_TS.xlsx
+++ b/pages/WR_progressions/Medals_Women_TS.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28025"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SamB\CNZPD\pages\WR_progressions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFF8707B-A114-4D72-9336-E3BCC544AD0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99FB80D6-FBA5-41B8-8A1E-F582D9E50A52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{60BF7A36-0D27-46A2-BCFD-CC0E6E4E1F78}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="8">
   <si>
     <t>Year</t>
   </si>
@@ -434,7 +434,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C1A844C-89A8-4AB0-8288-D746F85E52AB}">
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:I8"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="4.73046875" bestFit="1" customWidth="1"/>
@@ -468,81 +468,101 @@
         <v>2024</v>
       </c>
       <c r="B2" t="s">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C2" s="1">
-        <v>45.472000000000001</v>
+        <v>46.216999999999999</v>
       </c>
       <c r="D2" s="1">
-        <v>45.593000000000004</v>
+        <v>46.93</v>
       </c>
       <c r="E2" s="1">
-        <v>45.643999999999998</v>
+        <v>47.726999999999997</v>
       </c>
       <c r="F2" s="1">
-        <v>47.578000000000003</v>
+        <v>51.942</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A3">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3">
-        <v>46.072000000000003</v>
-      </c>
-      <c r="D3">
-        <v>46.466999999999999</v>
-      </c>
-      <c r="E3">
-        <v>46.679000000000002</v>
-      </c>
-      <c r="F3">
-        <v>47.436</v>
+        <v>7</v>
+      </c>
+      <c r="C3" s="1">
+        <v>45.472000000000001</v>
+      </c>
+      <c r="D3" s="1">
+        <v>45.593000000000004</v>
+      </c>
+      <c r="E3" s="1">
+        <v>45.643999999999998</v>
+      </c>
+      <c r="F3" s="1">
+        <v>47.578000000000003</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A4">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="B4" t="s">
         <v>2</v>
       </c>
       <c r="C4">
-        <v>46.573</v>
+        <v>46.072000000000003</v>
       </c>
       <c r="D4">
-        <v>46.643000000000001</v>
+        <v>46.466999999999999</v>
       </c>
       <c r="E4">
-        <v>46.985999999999997</v>
+        <v>46.679000000000002</v>
       </c>
       <c r="F4">
-        <v>48.73</v>
+        <v>47.436</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A5">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="B5" t="s">
         <v>2</v>
       </c>
       <c r="C5">
+        <v>46.573</v>
+      </c>
+      <c r="D5">
+        <v>46.643000000000001</v>
+      </c>
+      <c r="E5">
+        <v>46.985999999999997</v>
+      </c>
+      <c r="F5">
+        <v>48.73</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A6">
+        <v>2021</v>
+      </c>
+      <c r="B6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C6">
         <v>46.511000000000003</v>
       </c>
-      <c r="D5">
+      <c r="D6">
         <v>47.030999999999999</v>
       </c>
-      <c r="I5" s="1"/>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.45">
       <c r="I6" s="1"/>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.45">
       <c r="I7" s="1"/>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="I8" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/pages/WR_progressions/Medals_Women_TS.xlsx
+++ b/pages/WR_progressions/Medals_Women_TS.xlsx
@@ -1,20 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28025"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SamB\CNZPD\pages\WR_progressions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99FB80D6-FBA5-41B8-8A1E-F582D9E50A52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56986B69-D69A-427D-888B-580E6BF9E762}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{60BF7A36-0D27-46A2-BCFD-CC0E6E4E1F78}"/>
+    <workbookView xWindow="38280" yWindow="7470" windowWidth="29040" windowHeight="15720" xr2:uid="{60BF7A36-0D27-46A2-BCFD-CC0E6E4E1F78}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$H$22</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -36,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="12">
   <si>
     <t>Year</t>
   </si>
@@ -60,6 +63,18 @@
   </si>
   <si>
     <t>OLY</t>
+  </si>
+  <si>
+    <t>Date</t>
+  </si>
+  <si>
+    <t>NC</t>
+  </si>
+  <si>
+    <t>EC</t>
+  </si>
+  <si>
+    <t>DateSerial</t>
   </si>
 </sst>
 </file>
@@ -95,16 +110,39 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="3">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -434,137 +472,536 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C1A844C-89A8-4AB0-8288-D746F85E52AB}">
-  <dimension ref="A1:I8"/>
+  <dimension ref="A1:J20"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="4.73046875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="4.73046875" customWidth="1"/>
-    <col min="4" max="4" width="9.59765625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.73046875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.9296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.53125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6.73046875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.59765625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.73046875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.9296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="H1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A2">
+        <v>2025</v>
+      </c>
+      <c r="B2" s="2">
+        <v>45730</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2">
+        <v>45.777000000000001</v>
+      </c>
+      <c r="E2" s="1">
+        <v>46.079000000000001</v>
+      </c>
+      <c r="F2" s="1">
+        <v>46.366999999999997</v>
+      </c>
+      <c r="G2" s="1">
+        <v>49.487000000000002</v>
+      </c>
+      <c r="H2">
+        <v>45730</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A3">
+        <v>2025</v>
+      </c>
+      <c r="B3" s="2">
+        <v>45700</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3">
+        <v>46.832999999999998</v>
+      </c>
+      <c r="E3" s="1">
+        <v>47.107999999999997</v>
+      </c>
+      <c r="F3" s="1">
+        <v>47.167999999999999</v>
+      </c>
+      <c r="H3">
+        <v>45700</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A4">
         <v>2024</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B4" s="2">
+        <v>45581</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="1">
+      <c r="D4">
         <v>46.216999999999999</v>
       </c>
-      <c r="D2" s="1">
+      <c r="E4">
         <v>46.93</v>
       </c>
-      <c r="E2" s="1">
+      <c r="F4">
         <v>47.726999999999997</v>
       </c>
-      <c r="F2" s="1">
+      <c r="G4" s="1">
         <v>51.942</v>
       </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A3">
+      <c r="H4">
+        <v>45581</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A5">
         <v>2024</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B5" s="2">
+        <v>45540</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="1">
+      <c r="D5">
         <v>45.472000000000001</v>
       </c>
-      <c r="D3" s="1">
+      <c r="E5">
         <v>45.593000000000004</v>
       </c>
-      <c r="E3" s="1">
+      <c r="F5">
         <v>45.643999999999998</v>
       </c>
-      <c r="F3" s="1">
+      <c r="G5">
         <v>47.578000000000003</v>
       </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A4">
+      <c r="H5">
+        <v>45540</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A6">
+        <v>2024</v>
+      </c>
+      <c r="B6" s="2">
+        <v>45394</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D6">
+        <v>46.856000000000002</v>
+      </c>
+      <c r="E6">
+        <v>47.113</v>
+      </c>
+      <c r="F6">
+        <v>47.4</v>
+      </c>
+      <c r="G6">
+        <v>50.344000000000001</v>
+      </c>
+      <c r="H6">
+        <v>45394</v>
+      </c>
+      <c r="J6" s="1"/>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A7">
+        <v>2024</v>
+      </c>
+      <c r="B7" s="2">
+        <v>45366</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D7">
+        <v>46.277999999999999</v>
+      </c>
+      <c r="E7">
+        <v>46.923000000000002</v>
+      </c>
+      <c r="F7">
+        <v>47.316000000000003</v>
+      </c>
+      <c r="G7">
+        <v>48.097999999999999</v>
+      </c>
+      <c r="H7">
+        <v>45366</v>
+      </c>
+      <c r="J7" s="1"/>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A8">
+        <v>2024</v>
+      </c>
+      <c r="B8" s="2">
+        <v>45325</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D8">
+        <v>46.61</v>
+      </c>
+      <c r="E8">
+        <v>47.402999999999999</v>
+      </c>
+      <c r="F8">
+        <v>47.731999999999999</v>
+      </c>
+      <c r="G8">
+        <v>48.816000000000003</v>
+      </c>
+      <c r="H8">
+        <v>45325</v>
+      </c>
+      <c r="J8" s="1"/>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A9">
+        <v>2024</v>
+      </c>
+      <c r="B9" s="2">
+        <v>45301</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D9">
+        <v>46.316000000000003</v>
+      </c>
+      <c r="E9">
+        <v>46.377000000000002</v>
+      </c>
+      <c r="F9">
+        <v>47.173000000000002</v>
+      </c>
+      <c r="G9">
+        <v>49.718000000000004</v>
+      </c>
+      <c r="H9">
+        <v>45301</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A10">
         <v>2023</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B10" s="2">
+        <v>45141</v>
+      </c>
+      <c r="C10" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C4">
+      <c r="D10">
         <v>46.072000000000003</v>
       </c>
-      <c r="D4">
+      <c r="E10">
         <v>46.466999999999999</v>
       </c>
-      <c r="E4">
+      <c r="F10">
         <v>46.679000000000002</v>
       </c>
-      <c r="F4">
+      <c r="G10">
         <v>47.436</v>
       </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A5">
+      <c r="H10">
+        <v>45141</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A11">
+        <v>2023</v>
+      </c>
+      <c r="B11" s="2">
+        <v>45037</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D11">
+        <v>47.555</v>
+      </c>
+      <c r="E11">
+        <v>47.603000000000002</v>
+      </c>
+      <c r="F11">
+        <v>47.802</v>
+      </c>
+      <c r="H11">
+        <v>45037</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A12">
+        <v>2023</v>
+      </c>
+      <c r="B12" s="2">
+        <v>45000</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D12">
+        <v>46.854999999999997</v>
+      </c>
+      <c r="E12">
+        <v>47.097000000000001</v>
+      </c>
+      <c r="F12">
+        <v>47.37</v>
+      </c>
+      <c r="G12">
+        <v>49.045999999999999</v>
+      </c>
+      <c r="H12">
+        <v>45000</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A13">
+        <v>2023</v>
+      </c>
+      <c r="B13" s="2">
+        <v>44981</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D13">
+        <v>46.987000000000002</v>
+      </c>
+      <c r="E13">
+        <v>47.131999999999998</v>
+      </c>
+      <c r="F13">
+        <v>47.136000000000003</v>
+      </c>
+      <c r="G13">
+        <v>48.253999999999998</v>
+      </c>
+      <c r="H13">
+        <v>44981</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A14">
         <v>2022</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B14" s="2">
+        <v>44846</v>
+      </c>
+      <c r="C14" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C5">
+      <c r="D14">
         <v>46.573</v>
       </c>
-      <c r="D5">
+      <c r="E14">
         <v>46.643000000000001</v>
       </c>
-      <c r="E5">
+      <c r="F14">
         <v>46.985999999999997</v>
       </c>
-      <c r="F5">
+      <c r="G14">
         <v>48.73</v>
       </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A6">
+      <c r="H14">
+        <v>44846</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A15">
+        <v>2022</v>
+      </c>
+      <c r="B15" s="2">
+        <v>44749</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D15">
+        <v>47.218000000000004</v>
+      </c>
+      <c r="E15">
+        <v>47.390999999999998</v>
+      </c>
+      <c r="F15">
+        <v>47.722999999999999</v>
+      </c>
+      <c r="G15">
+        <v>53.718000000000004</v>
+      </c>
+      <c r="H15">
+        <v>44749</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A16">
+        <v>2022</v>
+      </c>
+      <c r="B16" s="2">
+        <v>44693</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D16">
+        <v>47.103000000000002</v>
+      </c>
+      <c r="E16">
+        <v>47.731000000000002</v>
+      </c>
+      <c r="F16">
+        <v>47.906999999999996</v>
+      </c>
+      <c r="G16">
+        <v>50.034999999999997</v>
+      </c>
+      <c r="H16">
+        <v>44693</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A17">
+        <v>2022</v>
+      </c>
+      <c r="B17" s="2">
+        <v>44672</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D17">
+        <v>47.713999999999999</v>
+      </c>
+      <c r="E17">
+        <v>47.847000000000001</v>
+      </c>
+      <c r="F17">
+        <v>48.042000000000002</v>
+      </c>
+      <c r="G17">
+        <v>48.784999999999997</v>
+      </c>
+      <c r="H17">
+        <v>44672</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A18">
         <v>2021</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B18" s="2">
+        <v>44489</v>
+      </c>
+      <c r="C18" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C6">
+      <c r="D18">
         <v>46.511000000000003</v>
       </c>
-      <c r="D6">
+      <c r="E18">
         <v>47.030999999999999</v>
       </c>
-      <c r="I6" s="1"/>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="I7" s="1"/>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="I8" s="1"/>
+      <c r="F18">
+        <v>48.362000000000002</v>
+      </c>
+      <c r="G18">
+        <v>55.652999999999999</v>
+      </c>
+      <c r="H18">
+        <v>44489</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A19">
+        <v>2021</v>
+      </c>
+      <c r="B19" s="2">
+        <v>44448</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D19">
+        <v>48.204999999999998</v>
+      </c>
+      <c r="E19">
+        <v>48.765999999999998</v>
+      </c>
+      <c r="F19">
+        <v>49.040999999999997</v>
+      </c>
+      <c r="H19">
+        <v>44448</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A20">
+        <v>2021</v>
+      </c>
+      <c r="B20" s="2">
+        <v>44385</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D20">
+        <v>47.374000000000002</v>
+      </c>
+      <c r="E20">
+        <v>48.938000000000002</v>
+      </c>
+      <c r="F20">
+        <v>49.768999999999998</v>
+      </c>
+      <c r="H20">
+        <v>44385</v>
+      </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:H22" xr:uid="{1C1A844C-89A8-4AB0-8288-D746F85E52AB}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H20">
+      <sortCondition descending="1" ref="B1:B22"/>
+    </sortState>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/pages/WR_progressions/Medals_Women_TS.xlsx
+++ b/pages/WR_progressions/Medals_Women_TS.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SamB\CNZPD\pages\WR_progressions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56986B69-D69A-427D-888B-580E6BF9E762}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17245094-9B91-46AE-BC64-C61FCB7DAFAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="7470" windowWidth="29040" windowHeight="15720" xr2:uid="{60BF7A36-0D27-46A2-BCFD-CC0E6E4E1F78}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{60BF7A36-0D27-46A2-BCFD-CC0E6E4E1F78}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$H$22</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$H$23</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="12">
   <si>
     <t>Year</t>
   </si>
@@ -120,29 +120,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="3">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-  </dxfs>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -472,7 +450,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C1A844C-89A8-4AB0-8288-D746F85E52AB}">
-  <dimension ref="A1:J20"/>
+  <dimension ref="A1:K21"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="4.73046875" bestFit="1" customWidth="1"/>
@@ -484,7 +462,7 @@
     <col min="8" max="8" width="9.9296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -510,391 +488,395 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A2">
         <v>2025</v>
       </c>
       <c r="B2" s="2">
-        <v>45730</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D2">
-        <v>45.777000000000001</v>
+        <v>45952</v>
+      </c>
+      <c r="C2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="1">
+        <v>45.808</v>
       </c>
       <c r="E2" s="1">
-        <v>46.079000000000001</v>
+        <v>45.947000000000003</v>
       </c>
       <c r="F2" s="1">
-        <v>46.366999999999997</v>
+        <v>46.988</v>
       </c>
       <c r="G2" s="1">
-        <v>49.487000000000002</v>
+        <v>48.122999999999998</v>
       </c>
       <c r="H2">
-        <v>45730</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.45">
+        <v>45952</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A3">
         <v>2025</v>
       </c>
       <c r="B3" s="2">
+        <v>45730</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3">
+        <v>45.777000000000001</v>
+      </c>
+      <c r="E3" s="1">
+        <v>46.079000000000001</v>
+      </c>
+      <c r="F3" s="1">
+        <v>46.366999999999997</v>
+      </c>
+      <c r="G3" s="1">
+        <v>49.487000000000002</v>
+      </c>
+      <c r="H3">
+        <v>45730</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A4">
+        <v>2025</v>
+      </c>
+      <c r="B4" s="2">
         <v>45700</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C4" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D3">
+      <c r="D4">
         <v>46.832999999999998</v>
       </c>
-      <c r="E3" s="1">
+      <c r="E4" s="1">
         <v>47.107999999999997</v>
       </c>
-      <c r="F3" s="1">
+      <c r="F4" s="1">
         <v>47.167999999999999</v>
       </c>
-      <c r="H3">
+      <c r="H4">
         <v>45700</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A4">
-        <v>2024</v>
-      </c>
-      <c r="B4" s="2">
-        <v>45581</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D4">
-        <v>46.216999999999999</v>
-      </c>
-      <c r="E4">
-        <v>46.93</v>
-      </c>
-      <c r="F4">
-        <v>47.726999999999997</v>
-      </c>
-      <c r="G4" s="1">
-        <v>51.942</v>
-      </c>
-      <c r="H4">
-        <v>45581</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A5">
         <v>2024</v>
       </c>
       <c r="B5" s="2">
-        <v>45540</v>
+        <v>45581</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D5">
-        <v>45.472000000000001</v>
+        <v>46.216999999999999</v>
       </c>
       <c r="E5">
-        <v>45.593000000000004</v>
+        <v>46.93</v>
       </c>
       <c r="F5">
-        <v>45.643999999999998</v>
-      </c>
-      <c r="G5">
-        <v>47.578000000000003</v>
+        <v>47.726999999999997</v>
+      </c>
+      <c r="G5" s="1">
+        <v>51.942</v>
       </c>
       <c r="H5">
-        <v>45540</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.45">
+        <v>45581</v>
+      </c>
+      <c r="K5" s="1"/>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A6">
         <v>2024</v>
       </c>
       <c r="B6" s="2">
-        <v>45394</v>
+        <v>45540</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D6">
-        <v>46.856000000000002</v>
+        <v>45.472000000000001</v>
       </c>
       <c r="E6">
-        <v>47.113</v>
+        <v>45.593000000000004</v>
       </c>
       <c r="F6">
-        <v>47.4</v>
+        <v>45.643999999999998</v>
       </c>
       <c r="G6">
-        <v>50.344000000000001</v>
+        <v>47.578000000000003</v>
       </c>
       <c r="H6">
-        <v>45394</v>
-      </c>
-      <c r="J6" s="1"/>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.45">
+        <v>45540</v>
+      </c>
+      <c r="K6" s="1"/>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A7">
         <v>2024</v>
       </c>
       <c r="B7" s="2">
-        <v>45366</v>
+        <v>45394</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D7">
-        <v>46.277999999999999</v>
+        <v>46.856000000000002</v>
       </c>
       <c r="E7">
-        <v>46.923000000000002</v>
+        <v>47.113</v>
       </c>
       <c r="F7">
-        <v>47.316000000000003</v>
+        <v>47.4</v>
       </c>
       <c r="G7">
-        <v>48.097999999999999</v>
+        <v>50.344000000000001</v>
       </c>
       <c r="H7">
-        <v>45366</v>
+        <v>45394</v>
       </c>
       <c r="J7" s="1"/>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="K7" s="1"/>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A8">
         <v>2024</v>
       </c>
       <c r="B8" s="2">
-        <v>45325</v>
+        <v>45366</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D8">
-        <v>46.61</v>
+        <v>46.277999999999999</v>
       </c>
       <c r="E8">
-        <v>47.402999999999999</v>
+        <v>46.923000000000002</v>
       </c>
       <c r="F8">
-        <v>47.731999999999999</v>
+        <v>47.316000000000003</v>
       </c>
       <c r="G8">
-        <v>48.816000000000003</v>
+        <v>48.097999999999999</v>
       </c>
       <c r="H8">
-        <v>45325</v>
+        <v>45366</v>
       </c>
       <c r="J8" s="1"/>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="K8" s="1"/>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A9">
         <v>2024</v>
       </c>
       <c r="B9" s="2">
+        <v>45325</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D9">
+        <v>46.61</v>
+      </c>
+      <c r="E9">
+        <v>47.402999999999999</v>
+      </c>
+      <c r="F9">
+        <v>47.731999999999999</v>
+      </c>
+      <c r="G9">
+        <v>48.816000000000003</v>
+      </c>
+      <c r="H9">
+        <v>45325</v>
+      </c>
+      <c r="J9" s="1"/>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A10">
+        <v>2024</v>
+      </c>
+      <c r="B10" s="2">
         <v>45301</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="C10" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D9">
+      <c r="D10">
         <v>46.316000000000003</v>
       </c>
-      <c r="E9">
+      <c r="E10">
         <v>46.377000000000002</v>
       </c>
-      <c r="F9">
+      <c r="F10">
         <v>47.173000000000002</v>
       </c>
-      <c r="G9">
+      <c r="G10">
         <v>49.718000000000004</v>
       </c>
-      <c r="H9">
+      <c r="H10">
         <v>45301</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A10">
-        <v>2023</v>
-      </c>
-      <c r="B10" s="2">
-        <v>45141</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D10">
-        <v>46.072000000000003</v>
-      </c>
-      <c r="E10">
-        <v>46.466999999999999</v>
-      </c>
-      <c r="F10">
-        <v>46.679000000000002</v>
-      </c>
-      <c r="G10">
-        <v>47.436</v>
-      </c>
-      <c r="H10">
-        <v>45141</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A11">
         <v>2023</v>
       </c>
       <c r="B11" s="2">
-        <v>45037</v>
+        <v>45141</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D11">
-        <v>47.555</v>
+        <v>46.072000000000003</v>
       </c>
       <c r="E11">
-        <v>47.603000000000002</v>
+        <v>46.466999999999999</v>
       </c>
       <c r="F11">
-        <v>47.802</v>
+        <v>46.679000000000002</v>
+      </c>
+      <c r="G11">
+        <v>47.436</v>
       </c>
       <c r="H11">
-        <v>45037</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.45">
+        <v>45141</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A12">
         <v>2023</v>
       </c>
       <c r="B12" s="2">
-        <v>45000</v>
+        <v>45037</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D12">
-        <v>46.854999999999997</v>
+        <v>47.555</v>
       </c>
       <c r="E12">
-        <v>47.097000000000001</v>
+        <v>47.603000000000002</v>
       </c>
       <c r="F12">
-        <v>47.37</v>
-      </c>
-      <c r="G12">
-        <v>49.045999999999999</v>
+        <v>47.802</v>
       </c>
       <c r="H12">
-        <v>45000</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.45">
+        <v>45037</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A13">
         <v>2023</v>
       </c>
       <c r="B13" s="2">
+        <v>45000</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D13">
+        <v>46.854999999999997</v>
+      </c>
+      <c r="E13">
+        <v>47.097000000000001</v>
+      </c>
+      <c r="F13">
+        <v>47.37</v>
+      </c>
+      <c r="G13">
+        <v>49.045999999999999</v>
+      </c>
+      <c r="H13">
+        <v>45000</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A14">
+        <v>2023</v>
+      </c>
+      <c r="B14" s="2">
         <v>44981</v>
       </c>
-      <c r="C13" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D13">
+      <c r="C14" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D14">
         <v>46.987000000000002</v>
       </c>
-      <c r="E13">
+      <c r="E14">
         <v>47.131999999999998</v>
       </c>
-      <c r="F13">
+      <c r="F14">
         <v>47.136000000000003</v>
       </c>
-      <c r="G13">
+      <c r="G14">
         <v>48.253999999999998</v>
       </c>
-      <c r="H13">
+      <c r="H14">
         <v>44981</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A14">
-        <v>2022</v>
-      </c>
-      <c r="B14" s="2">
-        <v>44846</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D14">
-        <v>46.573</v>
-      </c>
-      <c r="E14">
-        <v>46.643000000000001</v>
-      </c>
-      <c r="F14">
-        <v>46.985999999999997</v>
-      </c>
-      <c r="G14">
-        <v>48.73</v>
-      </c>
-      <c r="H14">
-        <v>44846</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A15">
         <v>2022</v>
       </c>
       <c r="B15" s="2">
-        <v>44749</v>
+        <v>44846</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D15">
-        <v>47.218000000000004</v>
+        <v>46.573</v>
       </c>
       <c r="E15">
-        <v>47.390999999999998</v>
+        <v>46.643000000000001</v>
       </c>
       <c r="F15">
-        <v>47.722999999999999</v>
+        <v>46.985999999999997</v>
       </c>
       <c r="G15">
-        <v>53.718000000000004</v>
+        <v>48.73</v>
       </c>
       <c r="H15">
-        <v>44749</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.45">
+        <v>44846</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A16">
         <v>2022</v>
       </c>
       <c r="B16" s="2">
-        <v>44693</v>
+        <v>44749</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D16">
-        <v>47.103000000000002</v>
+        <v>47.218000000000004</v>
       </c>
       <c r="E16">
-        <v>47.731000000000002</v>
+        <v>47.390999999999998</v>
       </c>
       <c r="F16">
-        <v>47.906999999999996</v>
+        <v>47.722999999999999</v>
       </c>
       <c r="G16">
-        <v>50.034999999999997</v>
+        <v>53.718000000000004</v>
       </c>
       <c r="H16">
-        <v>44693</v>
+        <v>44749</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.45">
@@ -902,51 +884,51 @@
         <v>2022</v>
       </c>
       <c r="B17" s="2">
-        <v>44672</v>
+        <v>44693</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D17">
-        <v>47.713999999999999</v>
+        <v>47.103000000000002</v>
       </c>
       <c r="E17">
-        <v>47.847000000000001</v>
+        <v>47.731000000000002</v>
       </c>
       <c r="F17">
-        <v>48.042000000000002</v>
+        <v>47.906999999999996</v>
       </c>
       <c r="G17">
-        <v>48.784999999999997</v>
+        <v>50.034999999999997</v>
       </c>
       <c r="H17">
-        <v>44672</v>
+        <v>44693</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A18">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="B18" s="2">
-        <v>44489</v>
+        <v>44672</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D18">
-        <v>46.511000000000003</v>
+        <v>47.713999999999999</v>
       </c>
       <c r="E18">
-        <v>47.030999999999999</v>
+        <v>47.847000000000001</v>
       </c>
       <c r="F18">
-        <v>48.362000000000002</v>
+        <v>48.042000000000002</v>
       </c>
       <c r="G18">
-        <v>55.652999999999999</v>
+        <v>48.784999999999997</v>
       </c>
       <c r="H18">
-        <v>44489</v>
+        <v>44672</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.45">
@@ -954,22 +936,25 @@
         <v>2021</v>
       </c>
       <c r="B19" s="2">
-        <v>44448</v>
+        <v>44489</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D19">
-        <v>48.204999999999998</v>
+        <v>46.511000000000003</v>
       </c>
       <c r="E19">
-        <v>48.765999999999998</v>
+        <v>47.030999999999999</v>
       </c>
       <c r="F19">
-        <v>49.040999999999997</v>
+        <v>48.362000000000002</v>
+      </c>
+      <c r="G19">
+        <v>55.652999999999999</v>
       </c>
       <c r="H19">
-        <v>44448</v>
+        <v>44489</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.45">
@@ -977,28 +962,51 @@
         <v>2021</v>
       </c>
       <c r="B20" s="2">
+        <v>44448</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D20">
+        <v>48.204999999999998</v>
+      </c>
+      <c r="E20">
+        <v>48.765999999999998</v>
+      </c>
+      <c r="F20">
+        <v>49.040999999999997</v>
+      </c>
+      <c r="H20">
+        <v>44448</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A21">
+        <v>2021</v>
+      </c>
+      <c r="B21" s="2">
         <v>44385</v>
       </c>
-      <c r="C20" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D20">
+      <c r="C21" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D21">
         <v>47.374000000000002</v>
       </c>
-      <c r="E20">
+      <c r="E21">
         <v>48.938000000000002</v>
       </c>
-      <c r="F20">
+      <c r="F21">
         <v>49.768999999999998</v>
       </c>
-      <c r="H20">
+      <c r="H21">
         <v>44385</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H22" xr:uid="{1C1A844C-89A8-4AB0-8288-D746F85E52AB}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H20">
-      <sortCondition descending="1" ref="B1:B22"/>
+  <autoFilter ref="A1:H23" xr:uid="{1C1A844C-89A8-4AB0-8288-D746F85E52AB}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H21">
+      <sortCondition descending="1" ref="B1:B23"/>
     </sortState>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/pages/WR_progressions/Medals_Women_TS.xlsx
+++ b/pages/WR_progressions/Medals_Women_TS.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SamB\CNZPD\pages\WR_progressions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17245094-9B91-46AE-BC64-C61FCB7DAFAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABAC0644-E2B8-4AB8-B135-9108DF633652}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{60BF7A36-0D27-46A2-BCFD-CC0E6E4E1F78}"/>
+    <workbookView xWindow="38280" yWindow="30" windowWidth="29040" windowHeight="15720" xr2:uid="{60BF7A36-0D27-46A2-BCFD-CC0E6E4E1F78}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$H$23</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$H$24</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="12">
   <si>
     <t>Year</t>
   </si>
@@ -98,7 +98,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -106,21 +106,123 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="12">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -450,7 +552,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C1A844C-89A8-4AB0-8288-D746F85E52AB}">
-  <dimension ref="A1:K21"/>
+  <dimension ref="A1:K22"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="4.73046875" bestFit="1" customWidth="1"/>
@@ -489,29 +591,29 @@
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A2">
-        <v>2025</v>
-      </c>
-      <c r="B2" s="2">
-        <v>45952</v>
-      </c>
-      <c r="C2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D2" s="1">
-        <v>45.808</v>
-      </c>
-      <c r="E2" s="1">
-        <v>45.947000000000003</v>
-      </c>
-      <c r="F2" s="1">
-        <v>46.988</v>
-      </c>
-      <c r="G2" s="1">
-        <v>48.122999999999998</v>
+      <c r="A2" s="3">
+        <v>2026</v>
+      </c>
+      <c r="B2" s="4">
+        <v>46129</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" s="3">
+        <v>46.744999999999997</v>
+      </c>
+      <c r="E2" s="3">
+        <v>46.956000000000003</v>
+      </c>
+      <c r="F2" s="3">
+        <v>47.137</v>
+      </c>
+      <c r="G2" s="3">
+        <v>48.378</v>
       </c>
       <c r="H2">
-        <v>45952</v>
+        <v>46129</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.45">
@@ -519,25 +621,25 @@
         <v>2025</v>
       </c>
       <c r="B3" s="2">
-        <v>45730</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D3">
-        <v>45.777000000000001</v>
+        <v>45952</v>
+      </c>
+      <c r="C3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D3" s="1">
+        <v>45.808</v>
       </c>
       <c r="E3" s="1">
-        <v>46.079000000000001</v>
+        <v>45.947000000000003</v>
       </c>
       <c r="F3" s="1">
-        <v>46.366999999999997</v>
+        <v>46.988</v>
       </c>
       <c r="G3" s="1">
-        <v>49.487000000000002</v>
+        <v>48.122999999999998</v>
       </c>
       <c r="H3">
-        <v>45730</v>
+        <v>45952</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.45">
@@ -545,75 +647,74 @@
         <v>2025</v>
       </c>
       <c r="B4" s="2">
-        <v>45700</v>
+        <v>45730</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D4">
-        <v>46.832999999999998</v>
+        <v>45.777000000000001</v>
       </c>
       <c r="E4" s="1">
-        <v>47.107999999999997</v>
+        <v>46.079000000000001</v>
       </c>
       <c r="F4" s="1">
-        <v>47.167999999999999</v>
+        <v>46.366999999999997</v>
+      </c>
+      <c r="G4" s="1">
+        <v>49.487000000000002</v>
       </c>
       <c r="H4">
-        <v>45700</v>
+        <v>45730</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A5">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B5" s="2">
-        <v>45581</v>
+        <v>45700</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D5">
-        <v>46.216999999999999</v>
-      </c>
-      <c r="E5">
-        <v>46.93</v>
-      </c>
-      <c r="F5">
-        <v>47.726999999999997</v>
-      </c>
-      <c r="G5" s="1">
-        <v>51.942</v>
+        <v>46.832999999999998</v>
+      </c>
+      <c r="E5" s="1">
+        <v>47.107999999999997</v>
+      </c>
+      <c r="F5" s="1">
+        <v>47.167999999999999</v>
       </c>
       <c r="H5">
-        <v>45581</v>
-      </c>
-      <c r="K5" s="1"/>
+        <v>45700</v>
+      </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A6">
         <v>2024</v>
       </c>
       <c r="B6" s="2">
-        <v>45540</v>
+        <v>45581</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D6">
-        <v>45.472000000000001</v>
+        <v>46.216999999999999</v>
       </c>
       <c r="E6">
-        <v>45.593000000000004</v>
+        <v>46.93</v>
       </c>
       <c r="F6">
-        <v>45.643999999999998</v>
-      </c>
-      <c r="G6">
-        <v>47.578000000000003</v>
+        <v>47.726999999999997</v>
+      </c>
+      <c r="G6" s="1">
+        <v>51.942</v>
       </c>
       <c r="H6">
-        <v>45540</v>
+        <v>45581</v>
       </c>
       <c r="K6" s="1"/>
     </row>
@@ -622,27 +723,26 @@
         <v>2024</v>
       </c>
       <c r="B7" s="2">
-        <v>45394</v>
+        <v>45540</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D7">
-        <v>46.856000000000002</v>
+        <v>45.472000000000001</v>
       </c>
       <c r="E7">
-        <v>47.113</v>
+        <v>45.593000000000004</v>
       </c>
       <c r="F7">
-        <v>47.4</v>
+        <v>45.643999999999998</v>
       </c>
       <c r="G7">
-        <v>50.344000000000001</v>
+        <v>47.578000000000003</v>
       </c>
       <c r="H7">
-        <v>45394</v>
-      </c>
-      <c r="J7" s="1"/>
+        <v>45540</v>
+      </c>
       <c r="K7" s="1"/>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.45">
@@ -650,25 +750,25 @@
         <v>2024</v>
       </c>
       <c r="B8" s="2">
-        <v>45366</v>
+        <v>45394</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D8">
-        <v>46.277999999999999</v>
+        <v>46.856000000000002</v>
       </c>
       <c r="E8">
-        <v>46.923000000000002</v>
+        <v>47.113</v>
       </c>
       <c r="F8">
-        <v>47.316000000000003</v>
+        <v>47.4</v>
       </c>
       <c r="G8">
-        <v>48.097999999999999</v>
+        <v>50.344000000000001</v>
       </c>
       <c r="H8">
-        <v>45366</v>
+        <v>45394</v>
       </c>
       <c r="J8" s="1"/>
       <c r="K8" s="1"/>
@@ -678,78 +778,80 @@
         <v>2024</v>
       </c>
       <c r="B9" s="2">
-        <v>45325</v>
+        <v>45366</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D9">
-        <v>46.61</v>
+        <v>46.277999999999999</v>
       </c>
       <c r="E9">
-        <v>47.402999999999999</v>
+        <v>46.923000000000002</v>
       </c>
       <c r="F9">
-        <v>47.731999999999999</v>
+        <v>47.316000000000003</v>
       </c>
       <c r="G9">
-        <v>48.816000000000003</v>
+        <v>48.097999999999999</v>
       </c>
       <c r="H9">
-        <v>45325</v>
+        <v>45366</v>
       </c>
       <c r="J9" s="1"/>
+      <c r="K9" s="1"/>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A10">
         <v>2024</v>
       </c>
       <c r="B10" s="2">
-        <v>45301</v>
+        <v>45325</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D10">
-        <v>46.316000000000003</v>
+        <v>46.61</v>
       </c>
       <c r="E10">
-        <v>46.377000000000002</v>
+        <v>47.402999999999999</v>
       </c>
       <c r="F10">
-        <v>47.173000000000002</v>
+        <v>47.731999999999999</v>
       </c>
       <c r="G10">
-        <v>49.718000000000004</v>
+        <v>48.816000000000003</v>
       </c>
       <c r="H10">
-        <v>45301</v>
-      </c>
+        <v>45325</v>
+      </c>
+      <c r="J10" s="1"/>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A11">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B11" s="2">
-        <v>45141</v>
+        <v>45301</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D11">
-        <v>46.072000000000003</v>
+        <v>46.316000000000003</v>
       </c>
       <c r="E11">
-        <v>46.466999999999999</v>
+        <v>46.377000000000002</v>
       </c>
       <c r="F11">
-        <v>46.679000000000002</v>
+        <v>47.173000000000002</v>
       </c>
       <c r="G11">
-        <v>47.436</v>
+        <v>49.718000000000004</v>
       </c>
       <c r="H11">
-        <v>45141</v>
+        <v>45301</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.45">
@@ -757,22 +859,25 @@
         <v>2023</v>
       </c>
       <c r="B12" s="2">
-        <v>45037</v>
+        <v>45141</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D12">
-        <v>47.555</v>
+        <v>46.072000000000003</v>
       </c>
       <c r="E12">
-        <v>47.603000000000002</v>
+        <v>46.466999999999999</v>
       </c>
       <c r="F12">
-        <v>47.802</v>
+        <v>46.679000000000002</v>
+      </c>
+      <c r="G12">
+        <v>47.436</v>
       </c>
       <c r="H12">
-        <v>45037</v>
+        <v>45141</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.45">
@@ -780,25 +885,22 @@
         <v>2023</v>
       </c>
       <c r="B13" s="2">
-        <v>45000</v>
+        <v>45037</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D13">
-        <v>46.854999999999997</v>
+        <v>47.555</v>
       </c>
       <c r="E13">
-        <v>47.097000000000001</v>
+        <v>47.603000000000002</v>
       </c>
       <c r="F13">
-        <v>47.37</v>
-      </c>
-      <c r="G13">
-        <v>49.045999999999999</v>
+        <v>47.802</v>
       </c>
       <c r="H13">
-        <v>45000</v>
+        <v>45037</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.45">
@@ -806,51 +908,51 @@
         <v>2023</v>
       </c>
       <c r="B14" s="2">
-        <v>44981</v>
+        <v>45000</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D14">
-        <v>46.987000000000002</v>
+        <v>46.854999999999997</v>
       </c>
       <c r="E14">
-        <v>47.131999999999998</v>
+        <v>47.097000000000001</v>
       </c>
       <c r="F14">
-        <v>47.136000000000003</v>
+        <v>47.37</v>
       </c>
       <c r="G14">
-        <v>48.253999999999998</v>
+        <v>49.045999999999999</v>
       </c>
       <c r="H14">
-        <v>44981</v>
+        <v>45000</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A15">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="B15" s="2">
-        <v>44846</v>
+        <v>44981</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D15">
-        <v>46.573</v>
+        <v>46.987000000000002</v>
       </c>
       <c r="E15">
-        <v>46.643000000000001</v>
+        <v>47.131999999999998</v>
       </c>
       <c r="F15">
-        <v>46.985999999999997</v>
+        <v>47.136000000000003</v>
       </c>
       <c r="G15">
-        <v>48.73</v>
+        <v>48.253999999999998</v>
       </c>
       <c r="H15">
-        <v>44846</v>
+        <v>44981</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.45">
@@ -858,25 +960,25 @@
         <v>2022</v>
       </c>
       <c r="B16" s="2">
-        <v>44749</v>
+        <v>44846</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D16">
-        <v>47.218000000000004</v>
+        <v>46.573</v>
       </c>
       <c r="E16">
-        <v>47.390999999999998</v>
+        <v>46.643000000000001</v>
       </c>
       <c r="F16">
-        <v>47.722999999999999</v>
+        <v>46.985999999999997</v>
       </c>
       <c r="G16">
-        <v>53.718000000000004</v>
+        <v>48.73</v>
       </c>
       <c r="H16">
-        <v>44749</v>
+        <v>44846</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.45">
@@ -884,25 +986,25 @@
         <v>2022</v>
       </c>
       <c r="B17" s="2">
-        <v>44693</v>
+        <v>44749</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D17">
-        <v>47.103000000000002</v>
+        <v>47.218000000000004</v>
       </c>
       <c r="E17">
-        <v>47.731000000000002</v>
+        <v>47.390999999999998</v>
       </c>
       <c r="F17">
-        <v>47.906999999999996</v>
+        <v>47.722999999999999</v>
       </c>
       <c r="G17">
-        <v>50.034999999999997</v>
+        <v>53.718000000000004</v>
       </c>
       <c r="H17">
-        <v>44693</v>
+        <v>44749</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.45">
@@ -910,51 +1012,51 @@
         <v>2022</v>
       </c>
       <c r="B18" s="2">
-        <v>44672</v>
+        <v>44693</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D18">
-        <v>47.713999999999999</v>
+        <v>47.103000000000002</v>
       </c>
       <c r="E18">
-        <v>47.847000000000001</v>
+        <v>47.731000000000002</v>
       </c>
       <c r="F18">
-        <v>48.042000000000002</v>
+        <v>47.906999999999996</v>
       </c>
       <c r="G18">
-        <v>48.784999999999997</v>
+        <v>50.034999999999997</v>
       </c>
       <c r="H18">
-        <v>44672</v>
+        <v>44693</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A19">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="B19" s="2">
-        <v>44489</v>
+        <v>44672</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D19">
-        <v>46.511000000000003</v>
+        <v>47.713999999999999</v>
       </c>
       <c r="E19">
-        <v>47.030999999999999</v>
+        <v>47.847000000000001</v>
       </c>
       <c r="F19">
-        <v>48.362000000000002</v>
+        <v>48.042000000000002</v>
       </c>
       <c r="G19">
-        <v>55.652999999999999</v>
+        <v>48.784999999999997</v>
       </c>
       <c r="H19">
-        <v>44489</v>
+        <v>44672</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.45">
@@ -962,22 +1064,25 @@
         <v>2021</v>
       </c>
       <c r="B20" s="2">
-        <v>44448</v>
+        <v>44489</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D20">
-        <v>48.204999999999998</v>
+        <v>46.511000000000003</v>
       </c>
       <c r="E20">
-        <v>48.765999999999998</v>
+        <v>47.030999999999999</v>
       </c>
       <c r="F20">
-        <v>49.040999999999997</v>
+        <v>48.362000000000002</v>
+      </c>
+      <c r="G20">
+        <v>55.652999999999999</v>
       </c>
       <c r="H20">
-        <v>44448</v>
+        <v>44489</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.45">
@@ -985,30 +1090,86 @@
         <v>2021</v>
       </c>
       <c r="B21" s="2">
+        <v>44448</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D21">
+        <v>48.204999999999998</v>
+      </c>
+      <c r="E21">
+        <v>48.765999999999998</v>
+      </c>
+      <c r="F21">
+        <v>49.040999999999997</v>
+      </c>
+      <c r="H21">
+        <v>44448</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A22">
+        <v>2021</v>
+      </c>
+      <c r="B22" s="2">
         <v>44385</v>
       </c>
-      <c r="C21" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D21">
+      <c r="C22" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D22">
         <v>47.374000000000002</v>
       </c>
-      <c r="E21">
+      <c r="E22">
         <v>48.938000000000002</v>
       </c>
-      <c r="F21">
+      <c r="F22">
         <v>49.768999999999998</v>
       </c>
-      <c r="H21">
+      <c r="H22">
         <v>44385</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H23" xr:uid="{1C1A844C-89A8-4AB0-8288-D746F85E52AB}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H21">
-      <sortCondition descending="1" ref="B1:B23"/>
+  <autoFilter ref="A1:H24" xr:uid="{1C1A844C-89A8-4AB0-8288-D746F85E52AB}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H22">
+      <sortCondition descending="1" ref="B1:B24"/>
     </sortState>
   </autoFilter>
+  <conditionalFormatting sqref="D2:F2">
+    <cfRule type="expression" dxfId="11" priority="10">
+      <formula>$E2="R1"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="10" priority="11">
+      <formula>$E2="F"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="9" priority="12">
+      <formula>$E2="Q"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G2">
+    <cfRule type="expression" dxfId="8" priority="7">
+      <formula>$E2="R1"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="7" priority="8">
+      <formula>$E2="F"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="6" priority="9">
+      <formula>$E2="Q"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A2:C2">
+    <cfRule type="expression" dxfId="5" priority="4">
+      <formula>$E2="R1"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="4" priority="5">
+      <formula>$E2="F"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="3" priority="6">
+      <formula>$E2="Q"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/pages/WR_progressions/Medals_Women_TS.xlsx
+++ b/pages/WR_progressions/Medals_Women_TS.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SamB\CNZPD\pages\WR_progressions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABAC0644-E2B8-4AB8-B135-9108DF633652}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D20651F0-FD3C-4F2D-8D8B-F073648A3DAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="30" windowWidth="29040" windowHeight="15720" xr2:uid="{60BF7A36-0D27-46A2-BCFD-CC0E6E4E1F78}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$H$24</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$H$25</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="12">
   <si>
     <t>Year</t>
   </si>
@@ -137,49 +137,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="12">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="6">
     <dxf>
       <fill>
         <patternFill>
@@ -552,7 +510,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C1A844C-89A8-4AB0-8288-D746F85E52AB}">
-  <dimension ref="A1:K22"/>
+  <dimension ref="A1:K23"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="4.73046875" bestFit="1" customWidth="1"/>
@@ -591,55 +549,55 @@
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A2" s="3">
+      <c r="A2">
         <v>2026</v>
       </c>
-      <c r="B2" s="4">
+      <c r="B2" s="2">
+        <v>46136</v>
+      </c>
+      <c r="C2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" s="3">
+        <v>46.564999999999998</v>
+      </c>
+      <c r="E2" s="3">
+        <v>47.064999999999998</v>
+      </c>
+      <c r="F2" s="3">
+        <v>47.790999999999997</v>
+      </c>
+      <c r="G2" s="3">
+        <v>48.688000000000002</v>
+      </c>
+      <c r="H2">
+        <v>46136</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A3" s="3">
+        <v>2026</v>
+      </c>
+      <c r="B3" s="4">
         <v>46129</v>
       </c>
-      <c r="C2" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D2" s="3">
+      <c r="C3" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="3">
         <v>46.744999999999997</v>
       </c>
-      <c r="E2" s="3">
+      <c r="E3" s="3">
         <v>46.956000000000003</v>
       </c>
-      <c r="F2" s="3">
+      <c r="F3" s="3">
         <v>47.137</v>
       </c>
-      <c r="G2" s="3">
+      <c r="G3" s="3">
         <v>48.378</v>
       </c>
-      <c r="H2">
+      <c r="H3">
         <v>46129</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A3">
-        <v>2025</v>
-      </c>
-      <c r="B3" s="2">
-        <v>45952</v>
-      </c>
-      <c r="C3" t="s">
-        <v>2</v>
-      </c>
-      <c r="D3" s="1">
-        <v>45.808</v>
-      </c>
-      <c r="E3" s="1">
-        <v>45.947000000000003</v>
-      </c>
-      <c r="F3" s="1">
-        <v>46.988</v>
-      </c>
-      <c r="G3" s="1">
-        <v>48.122999999999998</v>
-      </c>
-      <c r="H3">
-        <v>45952</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.45">
@@ -647,25 +605,25 @@
         <v>2025</v>
       </c>
       <c r="B4" s="2">
-        <v>45730</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D4">
-        <v>45.777000000000001</v>
+        <v>45952</v>
+      </c>
+      <c r="C4" t="s">
+        <v>2</v>
+      </c>
+      <c r="D4" s="1">
+        <v>45.808</v>
       </c>
       <c r="E4" s="1">
-        <v>46.079000000000001</v>
+        <v>45.947000000000003</v>
       </c>
       <c r="F4" s="1">
-        <v>46.366999999999997</v>
+        <v>46.988</v>
       </c>
       <c r="G4" s="1">
-        <v>49.487000000000002</v>
+        <v>48.122999999999998</v>
       </c>
       <c r="H4">
-        <v>45730</v>
+        <v>45952</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.45">
@@ -673,75 +631,74 @@
         <v>2025</v>
       </c>
       <c r="B5" s="2">
-        <v>45700</v>
+        <v>45730</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D5">
-        <v>46.832999999999998</v>
+        <v>45.777000000000001</v>
       </c>
       <c r="E5" s="1">
-        <v>47.107999999999997</v>
+        <v>46.079000000000001</v>
       </c>
       <c r="F5" s="1">
-        <v>47.167999999999999</v>
+        <v>46.366999999999997</v>
+      </c>
+      <c r="G5" s="1">
+        <v>49.487000000000002</v>
       </c>
       <c r="H5">
-        <v>45700</v>
+        <v>45730</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A6">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B6" s="2">
-        <v>45581</v>
+        <v>45700</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D6">
-        <v>46.216999999999999</v>
-      </c>
-      <c r="E6">
-        <v>46.93</v>
-      </c>
-      <c r="F6">
-        <v>47.726999999999997</v>
-      </c>
-      <c r="G6" s="1">
-        <v>51.942</v>
+        <v>46.832999999999998</v>
+      </c>
+      <c r="E6" s="1">
+        <v>47.107999999999997</v>
+      </c>
+      <c r="F6" s="1">
+        <v>47.167999999999999</v>
       </c>
       <c r="H6">
-        <v>45581</v>
-      </c>
-      <c r="K6" s="1"/>
+        <v>45700</v>
+      </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A7">
         <v>2024</v>
       </c>
       <c r="B7" s="2">
-        <v>45540</v>
+        <v>45581</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D7">
-        <v>45.472000000000001</v>
+        <v>46.216999999999999</v>
       </c>
       <c r="E7">
-        <v>45.593000000000004</v>
+        <v>46.93</v>
       </c>
       <c r="F7">
-        <v>45.643999999999998</v>
-      </c>
-      <c r="G7">
-        <v>47.578000000000003</v>
+        <v>47.726999999999997</v>
+      </c>
+      <c r="G7" s="1">
+        <v>51.942</v>
       </c>
       <c r="H7">
-        <v>45540</v>
+        <v>45581</v>
       </c>
       <c r="K7" s="1"/>
     </row>
@@ -750,27 +707,26 @@
         <v>2024</v>
       </c>
       <c r="B8" s="2">
-        <v>45394</v>
+        <v>45540</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D8">
-        <v>46.856000000000002</v>
+        <v>45.472000000000001</v>
       </c>
       <c r="E8">
-        <v>47.113</v>
+        <v>45.593000000000004</v>
       </c>
       <c r="F8">
-        <v>47.4</v>
+        <v>45.643999999999998</v>
       </c>
       <c r="G8">
-        <v>50.344000000000001</v>
+        <v>47.578000000000003</v>
       </c>
       <c r="H8">
-        <v>45394</v>
-      </c>
-      <c r="J8" s="1"/>
+        <v>45540</v>
+      </c>
       <c r="K8" s="1"/>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.45">
@@ -778,25 +734,25 @@
         <v>2024</v>
       </c>
       <c r="B9" s="2">
-        <v>45366</v>
+        <v>45394</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D9">
-        <v>46.277999999999999</v>
+        <v>46.856000000000002</v>
       </c>
       <c r="E9">
-        <v>46.923000000000002</v>
+        <v>47.113</v>
       </c>
       <c r="F9">
-        <v>47.316000000000003</v>
+        <v>47.4</v>
       </c>
       <c r="G9">
-        <v>48.097999999999999</v>
+        <v>50.344000000000001</v>
       </c>
       <c r="H9">
-        <v>45366</v>
+        <v>45394</v>
       </c>
       <c r="J9" s="1"/>
       <c r="K9" s="1"/>
@@ -806,78 +762,80 @@
         <v>2024</v>
       </c>
       <c r="B10" s="2">
-        <v>45325</v>
+        <v>45366</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D10">
-        <v>46.61</v>
+        <v>46.277999999999999</v>
       </c>
       <c r="E10">
-        <v>47.402999999999999</v>
+        <v>46.923000000000002</v>
       </c>
       <c r="F10">
-        <v>47.731999999999999</v>
+        <v>47.316000000000003</v>
       </c>
       <c r="G10">
-        <v>48.816000000000003</v>
+        <v>48.097999999999999</v>
       </c>
       <c r="H10">
-        <v>45325</v>
+        <v>45366</v>
       </c>
       <c r="J10" s="1"/>
+      <c r="K10" s="1"/>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A11">
         <v>2024</v>
       </c>
       <c r="B11" s="2">
-        <v>45301</v>
+        <v>45325</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D11">
-        <v>46.316000000000003</v>
+        <v>46.61</v>
       </c>
       <c r="E11">
-        <v>46.377000000000002</v>
+        <v>47.402999999999999</v>
       </c>
       <c r="F11">
-        <v>47.173000000000002</v>
+        <v>47.731999999999999</v>
       </c>
       <c r="G11">
-        <v>49.718000000000004</v>
+        <v>48.816000000000003</v>
       </c>
       <c r="H11">
-        <v>45301</v>
-      </c>
+        <v>45325</v>
+      </c>
+      <c r="J11" s="1"/>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A12">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B12" s="2">
-        <v>45141</v>
+        <v>45301</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D12">
-        <v>46.072000000000003</v>
+        <v>46.316000000000003</v>
       </c>
       <c r="E12">
-        <v>46.466999999999999</v>
+        <v>46.377000000000002</v>
       </c>
       <c r="F12">
-        <v>46.679000000000002</v>
+        <v>47.173000000000002</v>
       </c>
       <c r="G12">
-        <v>47.436</v>
+        <v>49.718000000000004</v>
       </c>
       <c r="H12">
-        <v>45141</v>
+        <v>45301</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.45">
@@ -885,22 +843,25 @@
         <v>2023</v>
       </c>
       <c r="B13" s="2">
-        <v>45037</v>
+        <v>45141</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D13">
-        <v>47.555</v>
+        <v>46.072000000000003</v>
       </c>
       <c r="E13">
-        <v>47.603000000000002</v>
+        <v>46.466999999999999</v>
       </c>
       <c r="F13">
-        <v>47.802</v>
+        <v>46.679000000000002</v>
+      </c>
+      <c r="G13">
+        <v>47.436</v>
       </c>
       <c r="H13">
-        <v>45037</v>
+        <v>45141</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.45">
@@ -908,25 +869,22 @@
         <v>2023</v>
       </c>
       <c r="B14" s="2">
-        <v>45000</v>
+        <v>45037</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D14">
-        <v>46.854999999999997</v>
+        <v>47.555</v>
       </c>
       <c r="E14">
-        <v>47.097000000000001</v>
+        <v>47.603000000000002</v>
       </c>
       <c r="F14">
-        <v>47.37</v>
-      </c>
-      <c r="G14">
-        <v>49.045999999999999</v>
+        <v>47.802</v>
       </c>
       <c r="H14">
-        <v>45000</v>
+        <v>45037</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.45">
@@ -934,51 +892,51 @@
         <v>2023</v>
       </c>
       <c r="B15" s="2">
-        <v>44981</v>
+        <v>45000</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D15">
-        <v>46.987000000000002</v>
+        <v>46.854999999999997</v>
       </c>
       <c r="E15">
-        <v>47.131999999999998</v>
+        <v>47.097000000000001</v>
       </c>
       <c r="F15">
-        <v>47.136000000000003</v>
+        <v>47.37</v>
       </c>
       <c r="G15">
-        <v>48.253999999999998</v>
+        <v>49.045999999999999</v>
       </c>
       <c r="H15">
-        <v>44981</v>
+        <v>45000</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A16">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="B16" s="2">
-        <v>44846</v>
+        <v>44981</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D16">
-        <v>46.573</v>
+        <v>46.987000000000002</v>
       </c>
       <c r="E16">
-        <v>46.643000000000001</v>
+        <v>47.131999999999998</v>
       </c>
       <c r="F16">
-        <v>46.985999999999997</v>
+        <v>47.136000000000003</v>
       </c>
       <c r="G16">
-        <v>48.73</v>
+        <v>48.253999999999998</v>
       </c>
       <c r="H16">
-        <v>44846</v>
+        <v>44981</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.45">
@@ -986,25 +944,25 @@
         <v>2022</v>
       </c>
       <c r="B17" s="2">
-        <v>44749</v>
+        <v>44846</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D17">
-        <v>47.218000000000004</v>
+        <v>46.573</v>
       </c>
       <c r="E17">
-        <v>47.390999999999998</v>
+        <v>46.643000000000001</v>
       </c>
       <c r="F17">
-        <v>47.722999999999999</v>
+        <v>46.985999999999997</v>
       </c>
       <c r="G17">
-        <v>53.718000000000004</v>
+        <v>48.73</v>
       </c>
       <c r="H17">
-        <v>44749</v>
+        <v>44846</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.45">
@@ -1012,25 +970,25 @@
         <v>2022</v>
       </c>
       <c r="B18" s="2">
-        <v>44693</v>
+        <v>44749</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D18">
-        <v>47.103000000000002</v>
+        <v>47.218000000000004</v>
       </c>
       <c r="E18">
-        <v>47.731000000000002</v>
+        <v>47.390999999999998</v>
       </c>
       <c r="F18">
-        <v>47.906999999999996</v>
+        <v>47.722999999999999</v>
       </c>
       <c r="G18">
-        <v>50.034999999999997</v>
+        <v>53.718000000000004</v>
       </c>
       <c r="H18">
-        <v>44693</v>
+        <v>44749</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.45">
@@ -1038,51 +996,51 @@
         <v>2022</v>
       </c>
       <c r="B19" s="2">
-        <v>44672</v>
+        <v>44693</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D19">
-        <v>47.713999999999999</v>
+        <v>47.103000000000002</v>
       </c>
       <c r="E19">
-        <v>47.847000000000001</v>
+        <v>47.731000000000002</v>
       </c>
       <c r="F19">
-        <v>48.042000000000002</v>
+        <v>47.906999999999996</v>
       </c>
       <c r="G19">
-        <v>48.784999999999997</v>
+        <v>50.034999999999997</v>
       </c>
       <c r="H19">
-        <v>44672</v>
+        <v>44693</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A20">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="B20" s="2">
-        <v>44489</v>
+        <v>44672</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D20">
-        <v>46.511000000000003</v>
+        <v>47.713999999999999</v>
       </c>
       <c r="E20">
-        <v>47.030999999999999</v>
+        <v>47.847000000000001</v>
       </c>
       <c r="F20">
-        <v>48.362000000000002</v>
+        <v>48.042000000000002</v>
       </c>
       <c r="G20">
-        <v>55.652999999999999</v>
+        <v>48.784999999999997</v>
       </c>
       <c r="H20">
-        <v>44489</v>
+        <v>44672</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.45">
@@ -1090,22 +1048,25 @@
         <v>2021</v>
       </c>
       <c r="B21" s="2">
-        <v>44448</v>
+        <v>44489</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D21">
-        <v>48.204999999999998</v>
+        <v>46.511000000000003</v>
       </c>
       <c r="E21">
-        <v>48.765999999999998</v>
+        <v>47.030999999999999</v>
       </c>
       <c r="F21">
-        <v>49.040999999999997</v>
+        <v>48.362000000000002</v>
+      </c>
+      <c r="G21">
+        <v>55.652999999999999</v>
       </c>
       <c r="H21">
-        <v>44448</v>
+        <v>44489</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.45">
@@ -1113,60 +1074,72 @@
         <v>2021</v>
       </c>
       <c r="B22" s="2">
+        <v>44448</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D22">
+        <v>48.204999999999998</v>
+      </c>
+      <c r="E22">
+        <v>48.765999999999998</v>
+      </c>
+      <c r="F22">
+        <v>49.040999999999997</v>
+      </c>
+      <c r="H22">
+        <v>44448</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A23">
+        <v>2021</v>
+      </c>
+      <c r="B23" s="2">
         <v>44385</v>
       </c>
-      <c r="C22" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D22">
+      <c r="C23" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D23">
         <v>47.374000000000002</v>
       </c>
-      <c r="E22">
+      <c r="E23">
         <v>48.938000000000002</v>
       </c>
-      <c r="F22">
+      <c r="F23">
         <v>49.768999999999998</v>
       </c>
-      <c r="H22">
+      <c r="H23">
         <v>44385</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H24" xr:uid="{1C1A844C-89A8-4AB0-8288-D746F85E52AB}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H22">
-      <sortCondition descending="1" ref="B1:B24"/>
+  <autoFilter ref="A1:H25" xr:uid="{1C1A844C-89A8-4AB0-8288-D746F85E52AB}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H23">
+      <sortCondition descending="1" ref="B1:B25"/>
     </sortState>
   </autoFilter>
-  <conditionalFormatting sqref="D2:F2">
-    <cfRule type="expression" dxfId="11" priority="10">
+  <conditionalFormatting sqref="A3:G3">
+    <cfRule type="expression" dxfId="5" priority="7">
+      <formula>$E3="R1"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="4" priority="8">
+      <formula>$E3="F"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="3" priority="9">
+      <formula>$E3="Q"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D2:G2">
+    <cfRule type="expression" dxfId="2" priority="1">
       <formula>$E2="R1"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="10" priority="11">
+    <cfRule type="expression" dxfId="1" priority="2">
       <formula>$E2="F"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="9" priority="12">
-      <formula>$E2="Q"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G2">
-    <cfRule type="expression" dxfId="8" priority="7">
-      <formula>$E2="R1"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="7" priority="8">
-      <formula>$E2="F"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="6" priority="9">
-      <formula>$E2="Q"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A2:C2">
-    <cfRule type="expression" dxfId="5" priority="4">
-      <formula>$E2="R1"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="4" priority="5">
-      <formula>$E2="F"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="3" priority="6">
+    <cfRule type="expression" dxfId="0" priority="3">
       <formula>$E2="Q"</formula>
     </cfRule>
   </conditionalFormatting>
